--- a/jira_export_2026-08-13.xlsx
+++ b/jira_export_2026-08-13.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>160 h</t>
+          <t>162 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -6113,7 +6113,7 @@
         <v>7</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>20</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L102" s="14" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -8692,7 +8692,7 @@
         <v>1053.15</v>
       </c>
       <c r="P113" s="18" t="n">
-        <v>11.35</v>
+        <v>11.11</v>
       </c>
     </row>
   </sheetData>
@@ -9380,16 +9380,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>13.25</v>
+        <v>14.25</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>1.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>88.5</v>
+        <v>90.5</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>22</v>
@@ -9399,7 +9399,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>

--- a/jira_export_2026-08-13.xlsx
+++ b/jira_export_2026-08-13.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>162 h</t>
+          <t>166 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheter par la CC</t>
+          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -2669,7 +2669,7 @@
         <v>2</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>16</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>1053.15</v>
       </c>
       <c r="P113" s="18" t="n">
-        <v>11.11</v>
+        <v>10.66</v>
       </c>
     </row>
   </sheetData>
@@ -9380,7 +9380,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>14.25</v>
@@ -9389,7 +9389,7 @@
         <v>1.25</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>90.5</v>
+        <v>94.5</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>22</v>
@@ -9399,7 +9399,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.7%</t>
         </is>
       </c>
     </row>

--- a/jira_export_2026-08-13.xlsx
+++ b/jira_export_2026-08-13.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>166 h</t>
+          <t>173 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P113"/>
+  <dimension ref="A1:P115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -4422,12 +4422,12 @@
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32565</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[CD 22] - Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t xml:space="preserve">[CONSEIL DEPARTEMENTAL DES COTES D'ARMOR] </t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Afficher les AP signé avant MEP WFS</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="G52" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H52" s="14" t="inlineStr">
@@ -4469,22 +4469,14 @@
         <v>4</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-32556</t>
-        </is>
-      </c>
-      <c r="M52" s="14" t="inlineStr">
-        <is>
-          <t>00162313</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L52" s="14" t="inlineStr"/>
+      <c r="M52" s="14" t="inlineStr"/>
       <c r="N52" s="15" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P52" s="15" t="n">
@@ -4494,32 +4486,32 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4529,32 +4521,32 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K53" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>2335</v>
+        <v>142.1</v>
       </c>
       <c r="O53" s="16" t="n">
         <v>0</v>
@@ -4566,27 +4558,27 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -4606,7 +4598,7 @@
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J54" s="14" t="n">
@@ -4617,16 +4609,16 @@
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>450</v>
+        <v>2335</v>
       </c>
       <c r="O54" s="16" t="n">
         <v>0</v>
@@ -4638,32 +4630,32 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4673,32 +4665,32 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O55" s="16" t="n">
         <v>0</v>
@@ -4710,28 +4702,32 @@
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="inlineStr"/>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -4741,32 +4737,32 @@
       </c>
       <c r="H56" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J56" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K56" s="14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>255</v>
+        <v>910</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4778,27 +4774,23 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
-        </is>
-      </c>
-      <c r="C57" s="11" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr"/>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
@@ -4825,22 +4817,22 @@
         <v>5</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="12" t="n">
+        <v>255</v>
+      </c>
+      <c r="O57" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P57" s="12" t="n">
@@ -4850,27 +4842,27 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -4885,34 +4877,34 @@
       </c>
       <c r="H58" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J58" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>590.15</v>
-      </c>
-      <c r="O58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P58" s="15" t="n">
@@ -4922,12 +4914,12 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
@@ -4937,12 +4929,12 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4957,12 +4949,12 @@
       </c>
       <c r="H59" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
@@ -4973,16 +4965,16 @@
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>1000</v>
+        <v>590.15</v>
       </c>
       <c r="O59" s="16" t="n">
         <v>0</v>
@@ -4994,32 +4986,32 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -5029,34 +5021,34 @@
       </c>
       <c r="H60" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K60" s="14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="O60" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P60" s="15" t="n">
@@ -5066,32 +5058,32 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G61" s="11" t="inlineStr">
@@ -5101,34 +5093,34 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I61" s="11" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J61" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>285</v>
-      </c>
-      <c r="O61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
@@ -5138,32 +5130,32 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31967</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU LOT -CD46</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -5178,7 +5170,7 @@
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>11/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
@@ -5189,16 +5181,16 @@
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31971</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00159863</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>1325</v>
+        <v>285</v>
       </c>
       <c r="O62" s="16" t="n">
         <v>0</v>
@@ -5210,12 +5202,12 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31967</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[DEPARTEMENT DU LOT -CD46] - Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
@@ -5225,12 +5217,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>DEPARTEMENT DU LOT -CD46</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>Réinstallation nouveau serveur de la base de test et prod ainsi que Montée de version test et prod</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5250,7 +5242,7 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>11/03/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
@@ -5261,16 +5253,16 @@
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31971</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159863</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>120</v>
+        <v>1325</v>
       </c>
       <c r="O63" s="16" t="n">
         <v>0</v>
@@ -5282,32 +5274,32 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -5317,7 +5309,7 @@
       </c>
       <c r="H64" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
@@ -5333,16 +5325,16 @@
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>588</v>
+        <v>120</v>
       </c>
       <c r="O64" s="16" t="n">
         <v>0</v>
@@ -5354,27 +5346,27 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
@@ -5389,32 +5381,32 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K65" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>203.5</v>
+        <v>588</v>
       </c>
       <c r="O65" s="16" t="n">
         <v>0</v>
@@ -5426,12 +5418,12 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -5441,12 +5433,12 @@
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5461,12 +5453,12 @@
       </c>
       <c r="H66" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J66" s="14" t="n">
@@ -5477,16 +5469,16 @@
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>300</v>
+        <v>203.5</v>
       </c>
       <c r="O66" s="16" t="n">
         <v>0</v>
@@ -5498,32 +5490,32 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -5533,32 +5525,32 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5570,12 +5562,12 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31528</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LILLE] - Màj carto</t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
@@ -5585,12 +5577,12 @@
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LILLE</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -5600,7 +5592,7 @@
       </c>
       <c r="G68" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H68" s="14" t="inlineStr">
@@ -5617,14 +5609,22 @@
         <v>6</v>
       </c>
       <c r="K68" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L68" s="14" t="inlineStr"/>
-      <c r="M68" s="14" t="inlineStr"/>
+        <v>5.75</v>
+      </c>
+      <c r="L68" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31546</t>
+        </is>
+      </c>
+      <c r="M68" s="14" t="inlineStr">
+        <is>
+          <t>00157816</t>
+        </is>
+      </c>
       <c r="N68" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="15" t="n">
+        <v>700</v>
+      </c>
+      <c r="O68" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P68" s="15" t="n">
@@ -5634,27 +5634,27 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31528</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LILLE] - Màj carto</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LILLE</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="G69" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
@@ -5674,29 +5674,21 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>6</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L69" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-31468</t>
-        </is>
-      </c>
-      <c r="M69" s="11" t="inlineStr">
-        <is>
-          <t>00157346</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L69" s="11" t="inlineStr"/>
+      <c r="M69" s="11" t="inlineStr"/>
       <c r="N69" s="12" t="n">
-        <v>416.475</v>
-      </c>
-      <c r="O69" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="12" t="n">
@@ -5706,32 +5698,32 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -5741,32 +5733,32 @@
       </c>
       <c r="H70" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
         <v>6</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N70" s="15" t="n">
-        <v>210</v>
+        <v>416.475</v>
       </c>
       <c r="O70" s="16" t="n">
         <v>0</v>
@@ -5778,12 +5770,12 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31319</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
@@ -5793,12 +5785,12 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LARMOR PLAGE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
@@ -5829,16 +5821,16 @@
       </c>
       <c r="L71" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31328</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
-          <t>00156518</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N71" s="12" t="n">
-        <v>281</v>
+        <v>210</v>
       </c>
       <c r="O71" s="16" t="n">
         <v>0</v>
@@ -5850,12 +5842,12 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31319</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LARMOR PLAGE] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
@@ -5865,12 +5857,12 @@
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LARMOR PLAGE</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -5890,7 +5882,7 @@
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
@@ -5901,16 +5893,16 @@
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31328</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156518</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>130</v>
+        <v>281</v>
       </c>
       <c r="O72" s="16" t="n">
         <v>0</v>
@@ -5922,12 +5914,12 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
@@ -5937,12 +5929,12 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
@@ -5962,7 +5954,7 @@
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
@@ -5973,16 +5965,16 @@
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O73" s="16" t="n">
         <v>0</v>
@@ -5994,12 +5986,12 @@
     <row r="74">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C74" s="14" t="inlineStr">
@@ -6009,12 +6001,12 @@
       </c>
       <c r="D74" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F74" s="14" t="inlineStr">
@@ -6034,27 +6026,27 @@
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J74" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K74" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O74" s="16" t="n">
         <v>0</v>
@@ -6066,32 +6058,32 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6101,32 +6093,32 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>690</v>
+        <v>140</v>
       </c>
       <c r="O75" s="16" t="n">
         <v>0</v>
@@ -6138,27 +6130,27 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
@@ -6178,29 +6170,29 @@
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0.08</v>
+        <v>3.75</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O76" s="15" t="n">
+        <v>690</v>
+      </c>
+      <c r="O76" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P76" s="15" t="n">
@@ -6261,18 +6253,18 @@
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>187.5</v>
-      </c>
-      <c r="O77" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P77" s="12" t="n">
@@ -6333,16 +6325,16 @@
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>787.5</v>
+        <v>187.5</v>
       </c>
       <c r="O78" s="16" t="n">
         <v>0</v>
@@ -6354,32 +6346,32 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Migration V2</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G79" s="11" t="inlineStr">
@@ -6389,32 +6381,32 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>725</v>
+        <v>787.5</v>
       </c>
       <c r="O79" s="16" t="n">
         <v>0</v>
@@ -6426,30 +6418,32 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E80" s="14" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E80" s="14" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -6459,34 +6453,34 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K80" s="14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O80" s="15" t="n">
+        <v>725</v>
+      </c>
+      <c r="O80" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P80" s="15" t="n">
@@ -6496,12 +6490,12 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
@@ -6511,13 +6505,11 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E81" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v/>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
@@ -6536,23 +6528,23 @@
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J81" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
@@ -6619,12 +6611,12 @@
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
@@ -6691,12 +6683,12 @@
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
@@ -6763,12 +6755,12 @@
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
@@ -6835,18 +6827,18 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>1320</v>
-      </c>
-      <c r="O85" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P85" s="12" t="n">
@@ -6856,12 +6848,12 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
@@ -6871,11 +6863,13 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E86" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E86" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
         <is>
@@ -6894,29 +6888,29 @@
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K86" s="14" t="n">
-        <v>4</v>
+        <v>0.1</v>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="15" t="n">
+        <v>1320</v>
+      </c>
+      <c r="O86" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P86" s="15" t="n">
@@ -6926,12 +6920,12 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
@@ -6941,7 +6935,7 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E87" s="11" t="n">
@@ -6964,29 +6958,29 @@
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O87" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P87" s="12" t="n">
@@ -6996,28 +6990,26 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24774</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[SETE] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SETE</t>
-        </is>
-      </c>
-      <c r="E88" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="n">
+        <v/>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
@@ -7036,29 +7028,29 @@
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
         <v>10</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27578</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>499043</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" s="15" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O88" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P88" s="15" t="n">
@@ -7068,27 +7060,27 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24216</t>
+          <t>PDMDEP-24774</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>MMM - LITTERALIS Script purge de données</t>
+          <t>[SETE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+          <t>COMMUNE DE SETE</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Script purge de données</t>
+          <t>Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -7098,27 +7090,35 @@
       </c>
       <c r="G89" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>10/09/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K89" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L89" s="11" t="inlineStr"/>
-      <c r="M89" s="11" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="L89" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27578</t>
+        </is>
+      </c>
+      <c r="M89" s="11" t="inlineStr">
+        <is>
+          <t>499043</t>
+        </is>
+      </c>
       <c r="N89" s="12" t="n">
         <v>0</v>
       </c>
@@ -7132,26 +7132,28 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E90" s="14" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E90" s="14" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
         <is>
@@ -7160,35 +7162,27 @@
       </c>
       <c r="G90" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H90" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K90" s="14" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="L90" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-27996</t>
-        </is>
-      </c>
-      <c r="M90" s="14" t="inlineStr">
-        <is>
-          <t>501219</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L90" s="14" t="inlineStr"/>
+      <c r="M90" s="14" t="inlineStr"/>
       <c r="N90" s="15" t="n">
         <v>0</v>
       </c>
@@ -7251,12 +7245,12 @@
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
@@ -7272,22 +7266,22 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E92" s="14" t="n">
@@ -7310,23 +7304,23 @@
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>1.19</v>
+        <v>0.38</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
@@ -7391,12 +7385,12 @@
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
@@ -7427,7 +7421,7 @@
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E94" s="14" t="n">
@@ -7461,12 +7455,12 @@
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
@@ -7497,7 +7491,7 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -7531,12 +7525,12 @@
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
@@ -7552,22 +7546,22 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E96" s="14" t="n">
@@ -7585,34 +7579,34 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K96" s="14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>401</v>
-      </c>
-      <c r="O96" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="15" t="n">
@@ -7622,22 +7616,22 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21249</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM] - Interface Pastell</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -7653,24 +7647,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H97" s="11" t="inlineStr"/>
+      <c r="H97" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K97" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L97" s="11" t="inlineStr"/>
-      <c r="M97" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L97" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27373</t>
+        </is>
+      </c>
+      <c r="M97" s="11" t="inlineStr">
+        <is>
+          <t>466234</t>
+        </is>
+      </c>
       <c r="N97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="12" t="n">
+        <v>401</v>
+      </c>
+      <c r="O97" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P97" s="12" t="n">
@@ -7680,22 +7686,22 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21249</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>[MONTPELLIER MMM] - Interface Pastell</t>
         </is>
       </c>
       <c r="E98" s="14" t="n">
@@ -7711,11 +7717,7 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H98" s="14" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H98" s="14" t="inlineStr"/>
       <c r="I98" s="14" t="inlineStr">
         <is>
           <t>23/04/2025</t>
@@ -7725,18 +7727,10 @@
         <v>16</v>
       </c>
       <c r="K98" s="14" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="L98" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28036</t>
-        </is>
-      </c>
-      <c r="M98" s="14" t="inlineStr">
-        <is>
-          <t>483799</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L98" s="14" t="inlineStr"/>
+      <c r="M98" s="14" t="inlineStr"/>
       <c r="N98" s="15" t="n">
         <v>0</v>
       </c>
@@ -7750,12 +7744,12 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
@@ -7765,7 +7759,7 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E99" s="11" t="n">
@@ -7783,34 +7777,34 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
         <v>16</v>
       </c>
       <c r="K99" s="11" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>230</v>
-      </c>
-      <c r="O99" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P99" s="12" t="n">
@@ -7820,22 +7814,22 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E100" s="14" t="n">
@@ -7848,27 +7842,39 @@
       </c>
       <c r="G100" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H100" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H100" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K100" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L100" s="14" t="inlineStr"/>
-      <c r="M100" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L100" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28034</t>
+        </is>
+      </c>
+      <c r="M100" s="14" t="inlineStr">
+        <is>
+          <t>475575</t>
+        </is>
+      </c>
       <c r="N100" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" s="15" t="n">
+        <v>230</v>
+      </c>
+      <c r="O100" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P100" s="15" t="n">
@@ -7878,22 +7884,22 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -7906,35 +7912,23 @@
       </c>
       <c r="G101" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H101" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H101" s="11" t="inlineStr"/>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
         <v>17</v>
       </c>
       <c r="K101" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="L101" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M101" s="11" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="L101" s="11" t="inlineStr"/>
+      <c r="M101" s="11" t="inlineStr"/>
       <c r="N101" s="12" t="n">
         <v>0</v>
       </c>
@@ -7948,12 +7942,12 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
@@ -7963,7 +7957,7 @@
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E102" s="14" t="n">
@@ -7976,7 +7970,7 @@
       </c>
       <c r="G102" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H102" s="14" t="inlineStr">
@@ -7986,17 +7980,25 @@
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L102" s="14" t="inlineStr"/>
-      <c r="M102" s="14" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="L102" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28027</t>
+        </is>
+      </c>
+      <c r="M102" s="14" t="inlineStr">
+        <is>
+          <t>470688</t>
+        </is>
+      </c>
       <c r="N102" s="15" t="n">
         <v>0</v>
       </c>
@@ -8010,12 +8012,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18196</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>[GENTILLY] - Litteralis Expert SAAS</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8025,7 +8027,7 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>Gentilly</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -8048,14 +8050,14 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>19/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
         <v>20</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="L103" s="11" t="inlineStr"/>
       <c r="M103" s="11" t="inlineStr"/>
@@ -8072,22 +8074,22 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18196</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[GENTILLY] - Litteralis Expert SAAS</t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Gentilly</t>
         </is>
       </c>
       <c r="E104" s="14" t="n">
@@ -8095,44 +8097,36 @@
       </c>
       <c r="F104" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G104" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H104" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>19/12/2024</t>
         </is>
       </c>
       <c r="J104" s="14" t="n">
         <v>20</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M104" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L104" s="14" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
       <c r="N104" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O104" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="15" t="n">
@@ -8142,22 +8136,22 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -8165,7 +8159,7 @@
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G105" s="11" t="inlineStr">
@@ -8175,12 +8169,12 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
@@ -8191,16 +8185,16 @@
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>557.145</v>
+        <v>240</v>
       </c>
       <c r="O105" s="16" t="n">
         <v>0</v>
@@ -8212,22 +8206,22 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8240,7 +8234,7 @@
       </c>
       <c r="G106" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H106" s="14" t="inlineStr">
@@ -8250,21 +8244,29 @@
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="L106" s="14" t="inlineStr"/>
-      <c r="M106" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L106" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M106" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N106" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O106" s="15" t="n">
+        <v>557.145</v>
+      </c>
+      <c r="O106" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P106" s="15" t="n">
@@ -8274,22 +8276,22 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -8312,25 +8314,17 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K107" s="11" t="n">
         <v>2.5</v>
       </c>
-      <c r="L107" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M107" s="11" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+      <c r="L107" s="11" t="inlineStr"/>
+      <c r="M107" s="11" t="inlineStr"/>
       <c r="N107" s="12" t="n">
         <v>0</v>
       </c>
@@ -8344,22 +8338,22 @@
     <row r="108">
       <c r="A108" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-14118</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>[SURESNES] Interface FAST-Parapheur</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
         <is>
-          <t>Suresnes</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E108" s="14" t="n">
@@ -8382,17 +8376,25 @@
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>01/02/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J108" s="14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K108" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L108" s="14" t="inlineStr"/>
-      <c r="M108" s="14" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L108" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M108" s="14" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N108" s="15" t="n">
         <v>0</v>
       </c>
@@ -8406,22 +8408,22 @@
     <row r="109">
       <c r="A109" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14118</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[SURESNES] Interface FAST-Parapheur</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Suresnes</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -8434,7 +8436,7 @@
       </c>
       <c r="G109" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H109" s="11" t="inlineStr">
@@ -8444,25 +8446,17 @@
       </c>
       <c r="I109" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>01/02/2024</t>
         </is>
       </c>
       <c r="J109" s="11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K109" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L109" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M109" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L109" s="11" t="inlineStr"/>
+      <c r="M109" s="11" t="inlineStr"/>
       <c r="N109" s="12" t="n">
         <v>0</v>
       </c>
@@ -8476,22 +8470,22 @@
     <row r="110">
       <c r="A110" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E110" s="14" t="n">
@@ -8504,17 +8498,17 @@
       </c>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H110" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J110" s="14" t="n">
@@ -8525,12 +8519,12 @@
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34532</t>
+          <t>PDMDEP-27990</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>412263</t>
+          <t>406296</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
@@ -8546,28 +8540,26 @@
     <row r="111">
       <c r="A111" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E111" s="11" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v/>
       </c>
       <c r="F111" s="11" t="inlineStr">
         <is>
@@ -8581,22 +8573,30 @@
       </c>
       <c r="H111" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I111" s="11" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J111" s="11" t="n">
         <v>35</v>
       </c>
       <c r="K111" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L111" s="11" t="inlineStr"/>
-      <c r="M111" s="11" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L111" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M111" s="11" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N111" s="12" t="n">
         <v>0</v>
       </c>
@@ -8610,24 +8610,26 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C112" s="14" t="inlineStr"/>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C112" s="14" t="inlineStr">
+        <is>
+          <t>Remy VINCENT</t>
+        </is>
+      </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E112" s="14" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="n">
+        <v/>
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
@@ -8646,14 +8648,14 @@
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="L112" s="14" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -8668,31 +8670,155 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="17" t="inlineStr">
+      <c r="A113" s="10" t="inlineStr">
+        <is>
+          <t>PDMDEP-12222</t>
+        </is>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H113" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="I113" s="11" t="inlineStr">
+        <is>
+          <t>04/09/2023</t>
+        </is>
+      </c>
+      <c r="J113" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="K113" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L113" s="11" t="inlineStr"/>
+      <c r="M113" s="11" t="inlineStr"/>
+      <c r="N113" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-11477</t>
+        </is>
+      </c>
+      <c r="B114" s="14" t="inlineStr">
+        <is>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C114" s="14" t="inlineStr"/>
+      <c r="D114" s="14" t="inlineStr">
+        <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E114" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F114" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G114" s="14" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H114" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I114" s="14" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J114" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K114" s="14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L114" s="14" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
+      <c r="N114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B113" s="17" t="inlineStr"/>
-      <c r="C113" s="17" t="inlineStr"/>
-      <c r="D113" s="17" t="inlineStr"/>
-      <c r="E113" s="17" t="inlineStr"/>
-      <c r="F113" s="17" t="inlineStr"/>
-      <c r="G113" s="17" t="inlineStr"/>
-      <c r="H113" s="17" t="inlineStr"/>
-      <c r="I113" s="17" t="inlineStr"/>
-      <c r="J113" s="17" t="inlineStr"/>
-      <c r="K113" s="17" t="inlineStr"/>
-      <c r="L113" s="17" t="inlineStr"/>
-      <c r="M113" s="17" t="inlineStr"/>
-      <c r="N113" s="18" t="n">
-        <v>67747.694</v>
-      </c>
-      <c r="O113" s="18" t="n">
+      <c r="B115" s="17" t="inlineStr"/>
+      <c r="C115" s="17" t="inlineStr"/>
+      <c r="D115" s="17" t="inlineStr"/>
+      <c r="E115" s="17" t="inlineStr"/>
+      <c r="F115" s="17" t="inlineStr"/>
+      <c r="G115" s="17" t="inlineStr"/>
+      <c r="H115" s="17" t="inlineStr"/>
+      <c r="I115" s="17" t="inlineStr"/>
+      <c r="J115" s="17" t="inlineStr"/>
+      <c r="K115" s="17" t="inlineStr"/>
+      <c r="L115" s="17" t="inlineStr"/>
+      <c r="M115" s="17" t="inlineStr"/>
+      <c r="N115" s="18" t="n">
+        <v>67747.69399999999</v>
+      </c>
+      <c r="O115" s="18" t="n">
         <v>1053.15</v>
       </c>
-      <c r="P113" s="18" t="n">
-        <v>10.66</v>
+      <c r="P115" s="18" t="n">
+        <v>10.1</v>
       </c>
     </row>
   </sheetData>
@@ -8806,6 +8932,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A113" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A114" r:id="rId110"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9380,16 +9508,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>14.25</v>
+        <v>17.25</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>1.25</v>
+        <v>2.75</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>94.5</v>
+        <v>100</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>22</v>
@@ -9399,7 +9527,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.6%</t>
         </is>
       </c>
     </row>
@@ -9441,7 +9569,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
